--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-diagnostic-report.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-diagnostic-report.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-10T06:36:19+00:00</t>
+    <t>2026-08-28T11:20:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3533,7 +3533,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>176</v>
       </c>
@@ -4565,7 +4565,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>232</v>
       </c>
@@ -4679,7 +4679,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>242</v>
       </c>
@@ -5249,7 +5249,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>284</v>
       </c>
@@ -5471,7 +5471,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>302</v>
       </c>
@@ -6039,7 +6039,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>327</v>
       </c>
@@ -6611,7 +6611,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>337</v>
       </c>
@@ -6725,7 +6725,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>339</v>
       </c>
@@ -7065,7 +7065,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>342</v>
       </c>
@@ -7411,7 +7411,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
         <v>369</v>
       </c>
@@ -9133,12 +9133,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN64">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-diagnostic-report.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-diagnostic-report.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.6.0</t>
+    <t>1.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T11:20:46+00:00</t>
+    <t>2026-08-28T12:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-diagnostic-report.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-diagnostic-report.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:05:03+00:00</t>
+    <t>2026-08-28T12:17:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>88</v>

--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-diagnostic-report.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-diagnostic-report.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:17:39+00:00</t>
+    <t>2026-08-31T14:07:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
